--- a/docs/export-templates/AI问书_XX出版社_答案反馈数据导出.xlsx
+++ b/docs/export-templates/AI问书_XX出版社_答案反馈数据导出.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="109">
   <si>
     <t>机构答案反馈</t>
   </si>
@@ -61,7 +61,7 @@
     <t>阿橙</t>
   </si>
   <si>
-    <t>会员</t>
+    <t>有效会员</t>
   </si>
   <si>
     <t>李医生 · 心血管分册</t>
@@ -85,6 +85,9 @@
     <t>林医森</t>
   </si>
   <si>
+    <t>宽限期（待续费）</t>
+  </si>
+  <si>
     <t>李医生 · 内科精要</t>
   </si>
   <si>
@@ -103,7 +106,7 @@
     <t>小满妈妈</t>
   </si>
   <si>
-    <t>非会员</t>
+    <t>未开通会员</t>
   </si>
   <si>
     <t>王老师 · 儿科学</t>
@@ -148,6 +151,9 @@
     <t>Cici</t>
   </si>
   <si>
+    <t>会员已过期</t>
+  </si>
+  <si>
     <t>机构 Agent</t>
   </si>
   <si>
@@ -278,6 +284,42 @@
   </si>
   <si>
     <t>2026-05-31 23:05</t>
+  </si>
+  <si>
+    <t>FB2027</t>
+  </si>
+  <si>
+    <t>拼音标注好像不对</t>
+  </si>
+  <si>
+    <t>感谢指正。经复核该字为多音字，已在答案中补充两种读音的使用场景。</t>
+  </si>
+  <si>
+    <t>柚子</t>
+  </si>
+  <si>
+    <t>故事姐姐 · 拼音王国</t>
+  </si>
+  <si>
+    <t>2026-08-04 19:22</t>
+  </si>
+  <si>
+    <t>FB2026</t>
+  </si>
+  <si>
+    <t>这道题的解析步骤跳步了</t>
+  </si>
+  <si>
+    <t>抱歉。已把该题解析补全为逐步推导，并标注每步依据的知识点。</t>
+  </si>
+  <si>
+    <t>刷题侠</t>
+  </si>
+  <si>
+    <t>解题助手 · 初中数学</t>
+  </si>
+  <si>
+    <t>2026-08-03 21:47</t>
   </si>
   <si>
     <t>FB2028</t>
@@ -762,7 +804,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -879,325 +921,377 @@
         <v>23</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
